--- a/guc/dist/20261028_創意個股模型_v0.1.2.xlsx
+++ b/guc/dist/20261028_創意個股模型_v0.1.2.xlsx
@@ -11683,26 +11683,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邁威爾模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">mrvl/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邁威爾個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -11806,26 +11806,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mediatek/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">mediatek/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12108,26 +12108,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邁威爾模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">mrvl/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邁威爾個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12210,26 +12210,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mediatek/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">mediatek/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12434,26 +12434,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邁威爾模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">mrvl/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邁威爾個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12536,26 +12536,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mediatek/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">mediatek/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -44670,26 +44670,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邁威爾模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">mrvl/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邁威爾個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -44708,26 +44708,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mediatek/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">mediatek/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
